--- a/public/file/shipment receive details.xlsx
+++ b/public/file/shipment receive details.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC426FF8-0453-4D55-80A8-4A0B3FFEE0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,9 +17,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Tracking No</t>
-  </si>
-  <si>
     <t>Receiver Name</t>
   </si>
   <si>
@@ -27,11 +25,14 @@
   <si>
     <t>Receiver Relationship</t>
   </si>
+  <si>
+    <t>Tracking Number</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -157,6 +158,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -192,6 +210,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -367,28 +402,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
